--- a/feedback_forms/001_support_interaction_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/001_support_interaction_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,8 +696,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -725,12 +725,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'effective'}</t>
+          <t>effective</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Effective'}</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'ineffective'}</t>
+          <t>ineffective</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Ineffective'}</t>
+          <t>Ineffective</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_ineffective'}</t>
+          <t>somewhat_ineffective</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat Ineffective'}</t>
+          <t>Somewhat Ineffective</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not Effective'}</t>
+          <t>Not Effective</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strong'}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strong'}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weak'}</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Weak'}</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
